--- a/etf_holdings/2026-08-24_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-24_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:27</t>
+          <t>2026-08-24 16:42:55</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:27</t>
+          <t>2026-08-24 16:42:55</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:27</t>
+          <t>2026-08-24 16:42:55</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:27</t>
+          <t>2026-08-24 16:42:55</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:27</t>
+          <t>2026-08-24 16:42:55</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:27</t>
+          <t>2026-08-24 16:42:55</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:27</t>
+          <t>2026-08-24 16:42:55</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:27</t>
+          <t>2026-08-24 16:42:55</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:27</t>
+          <t>2026-08-24 16:42:55</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:27</t>
+          <t>2026-08-24 16:42:55</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:27</t>
+          <t>2026-08-24 16:42:55</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:27</t>
+          <t>2026-08-24 16:42:55</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:27</t>
+          <t>2026-08-24 16:42:55</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:27</t>
+          <t>2026-08-24 16:42:55</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:27</t>
+          <t>2026-08-24 16:42:55</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:29</t>
+          <t>2026-08-24 16:42:56</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:29</t>
+          <t>2026-08-24 16:42:56</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:29</t>
+          <t>2026-08-24 16:42:56</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:29</t>
+          <t>2026-08-24 16:42:56</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:29</t>
+          <t>2026-08-24 16:42:56</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:29</t>
+          <t>2026-08-24 16:42:56</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:29</t>
+          <t>2026-08-24 16:42:56</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:29</t>
+          <t>2026-08-24 16:42:56</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:29</t>
+          <t>2026-08-24 16:42:56</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:29</t>
+          <t>2026-08-24 16:42:56</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:29</t>
+          <t>2026-08-24 16:42:56</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:29</t>
+          <t>2026-08-24 16:42:56</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:29</t>
+          <t>2026-08-24 16:42:56</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:29</t>
+          <t>2026-08-24 16:42:56</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:29</t>
+          <t>2026-08-24 16:42:56</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:30</t>
+          <t>2026-08-24 16:42:57</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:30</t>
+          <t>2026-08-24 16:42:57</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:30</t>
+          <t>2026-08-24 16:42:57</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:30</t>
+          <t>2026-08-24 16:42:57</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:30</t>
+          <t>2026-08-24 16:42:57</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:30</t>
+          <t>2026-08-24 16:42:57</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:30</t>
+          <t>2026-08-24 16:42:57</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:30</t>
+          <t>2026-08-24 16:42:57</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:30</t>
+          <t>2026-08-24 16:42:57</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:30</t>
+          <t>2026-08-24 16:42:57</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-24 16:25:30</t>
+          <t>2026-08-24 16:42:57</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">

--- a/etf_holdings/2026-08-24_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-24_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:55</t>
+          <t>2026-08-24 16:56:24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:55</t>
+          <t>2026-08-24 16:56:24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:55</t>
+          <t>2026-08-24 16:56:24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:55</t>
+          <t>2026-08-24 16:56:24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:55</t>
+          <t>2026-08-24 16:56:24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:55</t>
+          <t>2026-08-24 16:56:24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:55</t>
+          <t>2026-08-24 16:56:24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:55</t>
+          <t>2026-08-24 16:56:24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:55</t>
+          <t>2026-08-24 16:56:24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:55</t>
+          <t>2026-08-24 16:56:24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:55</t>
+          <t>2026-08-24 16:56:24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:55</t>
+          <t>2026-08-24 16:56:24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:55</t>
+          <t>2026-08-24 16:56:24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:55</t>
+          <t>2026-08-24 16:56:24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:55</t>
+          <t>2026-08-24 16:56:24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:56</t>
+          <t>2026-08-24 16:56:26</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:56</t>
+          <t>2026-08-24 16:56:26</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:56</t>
+          <t>2026-08-24 16:56:26</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:56</t>
+          <t>2026-08-24 16:56:26</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:56</t>
+          <t>2026-08-24 16:56:26</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:56</t>
+          <t>2026-08-24 16:56:26</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:56</t>
+          <t>2026-08-24 16:56:26</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:56</t>
+          <t>2026-08-24 16:56:26</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:56</t>
+          <t>2026-08-24 16:56:26</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:56</t>
+          <t>2026-08-24 16:56:26</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:56</t>
+          <t>2026-08-24 16:56:26</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:56</t>
+          <t>2026-08-24 16:56:26</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:56</t>
+          <t>2026-08-24 16:56:26</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:56</t>
+          <t>2026-08-24 16:56:26</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:56</t>
+          <t>2026-08-24 16:56:26</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:57</t>
+          <t>2026-08-24 16:56:27</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:57</t>
+          <t>2026-08-24 16:56:27</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:57</t>
+          <t>2026-08-24 16:56:27</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:57</t>
+          <t>2026-08-24 16:56:27</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:57</t>
+          <t>2026-08-24 16:56:27</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:57</t>
+          <t>2026-08-24 16:56:27</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:57</t>
+          <t>2026-08-24 16:56:27</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:57</t>
+          <t>2026-08-24 16:56:27</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:57</t>
+          <t>2026-08-24 16:56:27</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:57</t>
+          <t>2026-08-24 16:56:27</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:57</t>
+          <t>2026-08-24 16:56:27</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">

--- a/etf_holdings/2026-08-24_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-24_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:24</t>
+          <t>2026-08-24 19:46:57</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.30%260,000</t>
+          <t>9.02%260,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.30%</t>
+          <t>9.02%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:24</t>
+          <t>2026-08-24 19:46:57</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.51%1,306,000</t>
+          <t>7.47%1,306,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.51%</t>
+          <t>7.47%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:24</t>
+          <t>2026-08-24 19:46:57</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.84%1,001,000</t>
+          <t>6.88%1,001,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.84%</t>
+          <t>6.88%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:24</t>
+          <t>2026-08-24 19:46:57</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:24</t>
+          <t>2026-08-24 19:46:57</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-9.89%2050</t>
+          <t>-4.4%5430</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-9.89%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2050</v>
+        <v>5430</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.30%1,161,000</t>
+          <t>6.08%465,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.30%</t>
+          <t>6.08%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1161000</v>
+        <v>465000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.69%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:24</t>
+          <t>2026-08-24 19:46:57</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-4.4%5430</t>
+          <t>-9.89%2050</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-9.89%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5430</v>
+        <v>2050</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6.30%465,000</t>
+          <t>5.73%1,161,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6.30%</t>
+          <t>5.73%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>465000</v>
+        <v>1161000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:24</t>
+          <t>2026-08-24 19:46:57</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.21%1,074,000</t>
+          <t>5.35%1,074,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.21%</t>
+          <t>5.35%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:24</t>
+          <t>2026-08-24 19:46:57</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-4.01%5385</t>
+          <t>+5.05%1145</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-4.01%</t>
+          <t>+5.05%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5385</v>
+        <v>1145</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.59%343,000</t>
+          <t>4.49%1,630,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.59%</t>
+          <t>4.49%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>343000</v>
+        <v>1630000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:24</t>
+          <t>2026-08-24 19:46:57</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+5.05%1145</t>
+          <t>-4.01%5385</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+5.05%</t>
+          <t>-4.01%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1145</v>
+        <v>5385</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.24%1,630,000</t>
+          <t>4.45%343,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.24%</t>
+          <t>4.45%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1630000</v>
+        <v>343000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:24</t>
+          <t>2026-08-24 19:46:57</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.49%268,000</t>
+          <t>3.59%268,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.49%</t>
+          <t>3.59%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:24</t>
+          <t>2026-08-24 19:46:57</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1132,12 +1132,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.13%2,231,000</t>
+          <t>3.15%2,231,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:24</t>
+          <t>2026-08-24 19:46:57</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.03%7,245,000</t>
+          <t>3.06%7,245,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>3.06%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:24</t>
+          <t>2026-08-24 19:46:57</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.90%10,877,000</t>
+          <t>2.82%10,877,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.90%</t>
+          <t>2.82%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:24</t>
+          <t>2026-08-24 19:46:57</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2455全新</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-6.03%381.5</t>
+          <t>-0.86%1735</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-6.03%</t>
+          <t>-0.86%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>381.5</v>
+        <v>1735</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.67%2,753,000</t>
+          <t>2.64%632,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.64%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>2753000</v>
+        <v>632000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:24</t>
+          <t>2026-08-24 19:46:57</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>2455全新</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.86%1735</t>
+          <t>-6.03%381.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>-6.03%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1735</v>
+        <v>381.5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.64%632,000</t>
+          <t>2.53%2,753,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.64%</t>
+          <t>2.53%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>632000</v>
+        <v>2753000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:26</t>
+          <t>2026-08-24 19:46:58</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.54%2,682,000</t>
+          <t>2.51%2,682,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.51%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:26</t>
+          <t>2026-08-24 19:46:58</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-6.25%180</t>
+          <t>-0.66%3765</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-6.25%</t>
+          <t>-0.66%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>180</v>
+        <v>3765</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.49%5,445,000</t>
+          <t>2.41%266,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.41%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>5445000</v>
+        <v>266000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:26</t>
+          <t>2026-08-24 19:46:58</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-0.66%3765</t>
+          <t>-6.25%180</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>-6.25%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>3765</v>
+        <v>180</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.40%266,000</t>
+          <t>2.36%5,445,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>2.36%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>266000</v>
+        <v>5445000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:26</t>
+          <t>2026-08-24 19:46:58</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1620,12 +1620,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.19%164,000</t>
+          <t>2.12%164,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.12%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:26</t>
+          <t>2026-08-24 19:46:58</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1681,12 +1681,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.90%215,000</t>
+          <t>1.93%215,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.93%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:26</t>
+          <t>2026-08-24 19:46:58</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.63%844,013</t>
+          <t>1.61%844,013</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.61%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:26</t>
+          <t>2026-08-24 19:46:58</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.15%77,000</t>
+          <t>1.17%77,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:26</t>
+          <t>2026-08-24 19:46:58</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:26</t>
+          <t>2026-08-24 19:46:58</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.00%716,000</t>
+          <t>1.02%716,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:26</t>
+          <t>2026-08-24 19:46:58</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1986,12 +1986,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.81%300,000</t>
+          <t>0.82%300,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.82%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:26</t>
+          <t>2026-08-24 19:46:58</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,25 +2029,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6213聯茂</t>
+          <t>6139亞翔</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-5.95%482.5</t>
+          <t>-0.52%758</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-5.95%</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>482.5</v>
+        <v>758</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.46%373,000</t>
+          <t>0.46%250,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2056,11 +2056,11 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>373000</v>
+        <v>250000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:26</t>
+          <t>2026-08-24 19:46:58</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>6139亞翔</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-0.52%758</t>
+          <t>+9.96%287</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>+9.96%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>758</v>
+        <v>287</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.45%250,000</t>
+          <t>0.46%659,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>250000</v>
+        <v>659000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:26</t>
+          <t>2026-08-24 19:46:58</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,25 +2151,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>2357華碩</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-5.31%2765</t>
+          <t>+0.22%923</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-5.31%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2765</v>
+        <v>923</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.44%63,000</t>
+          <t>0.44%196,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2178,11 +2178,11 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>63000</v>
+        <v>196000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:26</t>
+          <t>2026-08-24 19:46:58</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,25 +2212,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2357華碩</t>
+          <t>6213聯茂</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+0.22%923</t>
+          <t>-5.95%482.5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>-5.95%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>923</v>
+        <v>482.5</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.43%196,000</t>
+          <t>0.43%373,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2239,11 +2239,11 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>196000</v>
+        <v>373000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:26</t>
+          <t>2026-08-24 19:46:58</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,25 +2273,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-4.45%5155</t>
+          <t>-5.31%2765</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-4.45%</t>
+          <t>-5.31%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>5155</v>
+        <v>2765</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.42%33,000</t>
+          <t>0.42%63,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>33000</v>
+        <v>63000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:27</t>
+          <t>2026-08-24 19:46:59</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.41%508,000</t>
+          <t>0.42%508,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:27</t>
+          <t>2026-08-24 19:46:59</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,25 +2395,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>8150南茂</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+9.96%287</t>
+          <t>+1.15%87.7</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>+1.15%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>287</v>
+        <v>87.7</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.41%659,000</t>
+          <t>0.41%1,957,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2422,11 +2422,11 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>659000</v>
+        <v>1957000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:27</t>
+          <t>2026-08-24 19:46:59</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>8150南茂</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+1.15%87.7</t>
+          <t>-4.45%5155</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+1.15%</t>
+          <t>-4.45%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>87.7</v>
+        <v>5155</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.40%1,957,000</t>
+          <t>0.41%33,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>1957000</v>
+        <v>33000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:27</t>
+          <t>2026-08-24 19:46:59</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,25 +2517,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>3026禾伸堂</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-2.68%1455</t>
+          <t>+0.63%643</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-2.68%</t>
+          <t>+0.63%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1455</v>
+        <v>643</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.40%113,000</t>
+          <t>0.40%261,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2544,11 +2544,11 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>113000</v>
+        <v>261000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:27</t>
+          <t>2026-08-24 19:46:59</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:27</t>
+          <t>2026-08-24 19:46:59</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,25 +2639,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3026禾伸堂</t>
+          <t>2404漢唐</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+0.63%643</t>
+          <t>+0.47%1065</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+0.63%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>643</v>
+        <v>1065</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.40%261,000</t>
+          <t>0.40%155,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>261000</v>
+        <v>155000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:27</t>
+          <t>2026-08-24 19:46:59</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2404漢唐</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+0.47%1065</t>
+          <t>-2.68%1455</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>-2.68%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1065</v>
+        <v>1455</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.39%155,000</t>
+          <t>0.40%113,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>155000</v>
+        <v>113000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:27</t>
+          <t>2026-08-24 19:46:59</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2779,12 +2779,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.38%134,000</t>
+          <t>0.39%134,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:27</t>
+          <t>2026-08-24 19:46:59</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:27</t>
+          <t>2026-08-24 19:46:59</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2901,12 +2901,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.36%98,000</t>
+          <t>0.37%98,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:27</t>
+          <t>2026-08-24 19:46:59</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">

--- a/etf_holdings/2026-08-24_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-24_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:57</t>
+          <t>2026-08-24 19:59:41</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:57</t>
+          <t>2026-08-24 19:59:41</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:57</t>
+          <t>2026-08-24 19:59:41</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:57</t>
+          <t>2026-08-24 19:59:41</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:57</t>
+          <t>2026-08-24 19:59:41</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:57</t>
+          <t>2026-08-24 19:59:41</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:57</t>
+          <t>2026-08-24 19:59:41</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:57</t>
+          <t>2026-08-24 19:59:41</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:57</t>
+          <t>2026-08-24 19:59:41</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:57</t>
+          <t>2026-08-24 19:59:41</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:57</t>
+          <t>2026-08-24 19:59:41</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:57</t>
+          <t>2026-08-24 19:59:41</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:57</t>
+          <t>2026-08-24 19:59:41</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:57</t>
+          <t>2026-08-24 19:59:41</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:57</t>
+          <t>2026-08-24 19:59:41</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:58</t>
+          <t>2026-08-24 19:59:42</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:58</t>
+          <t>2026-08-24 19:59:42</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:58</t>
+          <t>2026-08-24 19:59:42</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:58</t>
+          <t>2026-08-24 19:59:42</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:58</t>
+          <t>2026-08-24 19:59:42</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:58</t>
+          <t>2026-08-24 19:59:42</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:58</t>
+          <t>2026-08-24 19:59:42</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:58</t>
+          <t>2026-08-24 19:59:42</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:58</t>
+          <t>2026-08-24 19:59:42</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:58</t>
+          <t>2026-08-24 19:59:42</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:58</t>
+          <t>2026-08-24 19:59:42</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:58</t>
+          <t>2026-08-24 19:59:42</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:58</t>
+          <t>2026-08-24 19:59:42</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:58</t>
+          <t>2026-08-24 19:59:42</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:58</t>
+          <t>2026-08-24 19:59:42</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:59</t>
+          <t>2026-08-24 19:59:43</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:59</t>
+          <t>2026-08-24 19:59:43</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:59</t>
+          <t>2026-08-24 19:59:43</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:59</t>
+          <t>2026-08-24 19:59:43</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:59</t>
+          <t>2026-08-24 19:59:43</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:59</t>
+          <t>2026-08-24 19:59:43</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:59</t>
+          <t>2026-08-24 19:59:43</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:59</t>
+          <t>2026-08-24 19:59:43</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:59</t>
+          <t>2026-08-24 19:59:43</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:59</t>
+          <t>2026-08-24 19:59:43</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:59</t>
+          <t>2026-08-24 19:59:43</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">

--- a/etf_holdings/2026-08-24_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-24_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:41</t>
+          <t>2026-08-24 20:04:53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:41</t>
+          <t>2026-08-24 20:04:53</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:41</t>
+          <t>2026-08-24 20:04:53</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:41</t>
+          <t>2026-08-24 20:04:53</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:41</t>
+          <t>2026-08-24 20:04:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:41</t>
+          <t>2026-08-24 20:04:53</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:41</t>
+          <t>2026-08-24 20:04:53</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:41</t>
+          <t>2026-08-24 20:04:53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:41</t>
+          <t>2026-08-24 20:04:53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:41</t>
+          <t>2026-08-24 20:04:53</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:41</t>
+          <t>2026-08-24 20:04:53</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:41</t>
+          <t>2026-08-24 20:04:53</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:41</t>
+          <t>2026-08-24 20:04:53</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:41</t>
+          <t>2026-08-24 20:04:53</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:41</t>
+          <t>2026-08-24 20:04:53</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:42</t>
+          <t>2026-08-24 20:04:55</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:42</t>
+          <t>2026-08-24 20:04:55</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:42</t>
+          <t>2026-08-24 20:04:55</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:42</t>
+          <t>2026-08-24 20:04:55</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:42</t>
+          <t>2026-08-24 20:04:55</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:42</t>
+          <t>2026-08-24 20:04:55</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:42</t>
+          <t>2026-08-24 20:04:55</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:42</t>
+          <t>2026-08-24 20:04:55</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:42</t>
+          <t>2026-08-24 20:04:55</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:42</t>
+          <t>2026-08-24 20:04:55</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:42</t>
+          <t>2026-08-24 20:04:55</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:42</t>
+          <t>2026-08-24 20:04:55</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:42</t>
+          <t>2026-08-24 20:04:55</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:42</t>
+          <t>2026-08-24 20:04:55</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:42</t>
+          <t>2026-08-24 20:04:55</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:43</t>
+          <t>2026-08-24 20:04:56</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:43</t>
+          <t>2026-08-24 20:04:56</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:43</t>
+          <t>2026-08-24 20:04:56</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:43</t>
+          <t>2026-08-24 20:04:56</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:43</t>
+          <t>2026-08-24 20:04:56</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:43</t>
+          <t>2026-08-24 20:04:56</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:43</t>
+          <t>2026-08-24 20:04:56</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:43</t>
+          <t>2026-08-24 20:04:56</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:43</t>
+          <t>2026-08-24 20:04:56</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:43</t>
+          <t>2026-08-24 20:04:56</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:43</t>
+          <t>2026-08-24 20:04:56</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">

--- a/etf_holdings/2026-08-24_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-24_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:53</t>
+          <t>2026-08-24 23:04:16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:53</t>
+          <t>2026-08-24 23:04:16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:53</t>
+          <t>2026-08-24 23:04:16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:53</t>
+          <t>2026-08-24 23:04:16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:53</t>
+          <t>2026-08-24 23:04:16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:53</t>
+          <t>2026-08-24 23:04:16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:53</t>
+          <t>2026-08-24 23:04:16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:53</t>
+          <t>2026-08-24 23:04:16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:53</t>
+          <t>2026-08-24 23:04:16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:53</t>
+          <t>2026-08-24 23:04:16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:53</t>
+          <t>2026-08-24 23:04:16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:53</t>
+          <t>2026-08-24 23:04:16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:53</t>
+          <t>2026-08-24 23:04:16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:53</t>
+          <t>2026-08-24 23:04:16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:53</t>
+          <t>2026-08-24 23:04:16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:55</t>
+          <t>2026-08-24 23:04:17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:55</t>
+          <t>2026-08-24 23:04:17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:55</t>
+          <t>2026-08-24 23:04:17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:55</t>
+          <t>2026-08-24 23:04:17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:55</t>
+          <t>2026-08-24 23:04:17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:55</t>
+          <t>2026-08-24 23:04:17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:55</t>
+          <t>2026-08-24 23:04:17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:55</t>
+          <t>2026-08-24 23:04:17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:55</t>
+          <t>2026-08-24 23:04:17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:55</t>
+          <t>2026-08-24 23:04:17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:55</t>
+          <t>2026-08-24 23:04:17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:55</t>
+          <t>2026-08-24 23:04:17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:55</t>
+          <t>2026-08-24 23:04:17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:55</t>
+          <t>2026-08-24 23:04:17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:55</t>
+          <t>2026-08-24 23:04:17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:56</t>
+          <t>2026-08-24 23:04:18</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:56</t>
+          <t>2026-08-24 23:04:18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:56</t>
+          <t>2026-08-24 23:04:18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:56</t>
+          <t>2026-08-24 23:04:18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:56</t>
+          <t>2026-08-24 23:04:18</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:56</t>
+          <t>2026-08-24 23:04:18</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:56</t>
+          <t>2026-08-24 23:04:18</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:56</t>
+          <t>2026-08-24 23:04:18</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:56</t>
+          <t>2026-08-24 23:04:18</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:56</t>
+          <t>2026-08-24 23:04:18</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:56</t>
+          <t>2026-08-24 23:04:18</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
